--- a/data/trans_dic/IP2905_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna</t>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,94; 63,55</t>
+          <t>47,57; 62,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,78; 63,27</t>
+          <t>41,53; 64,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,24; 61,14</t>
+          <t>46,57; 60,39</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,16; 63,18</t>
+          <t>49,61; 62,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,77; 61,93</t>
+          <t>49,62; 61,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,85; 60,46</t>
+          <t>50,71; 59,99</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,36; 49,25</t>
+          <t>34,34; 48,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,38; 52,18</t>
+          <t>35,89; 51,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,75; 48,34</t>
+          <t>38,01; 48,14</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,49; 52,93</t>
+          <t>39,24; 52,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,85; 57,9</t>
+          <t>44,36; 57,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,35; 54,03</t>
+          <t>44,05; 53,36</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,94; 53,39</t>
+          <t>46,03; 53,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,13; 54,86</t>
+          <t>47,06; 54,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,7; 52,83</t>
+          <t>47,79; 52,99</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>62751</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70151</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>132903</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>53776; 71105</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56626; 88197</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>116159; 150629</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>104033</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>136122</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>240155</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>91787; 116305</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122270; 150934</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>218774; 258796</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>66055</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80116</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146171</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>54982; 78006</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>65018; 94024</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>129701; 164283</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>74233</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>89692</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>163926</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>62927; 83932</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>77691; 101496</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>147801; 179048</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>307072</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>376082</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>683154</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>284750; 328568</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>347770; 404953</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>648831; 719338</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2905_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,57; 62,89</t>
+          <t>47,62; 62,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,53; 64,68</t>
+          <t>41,26; 65,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,57; 60,39</t>
+          <t>46,88; 60,83</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,61; 62,86</t>
+          <t>49,9; 63,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,62; 61,25</t>
+          <t>48,92; 60,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,71; 59,99</t>
+          <t>51,04; 60,43</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,34; 48,72</t>
+          <t>34,26; 48,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,89; 51,9</t>
+          <t>37,11; 52,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,01; 48,14</t>
+          <t>37,7; 48,18</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,24; 52,33</t>
+          <t>40,17; 53,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,36; 57,95</t>
+          <t>44,51; 57,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,05; 53,36</t>
+          <t>43,85; 53,34</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,03; 53,12</t>
+          <t>46,3; 53,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,06; 54,79</t>
+          <t>47,2; 54,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,79; 52,99</t>
+          <t>47,61; 52,98</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53776; 71105</t>
+          <t>53836; 70596</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56626; 88197</t>
+          <t>56261; 88911</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116159; 150629</t>
+          <t>116911; 151727</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91787; 116305</t>
+          <t>92315; 116820</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>122270; 150934</t>
+          <t>120551; 149270</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218774; 258796</t>
+          <t>220178; 260726</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54982; 78006</t>
+          <t>54851; 78330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65018; 94024</t>
+          <t>67219; 94609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129701; 164283</t>
+          <t>128656; 164408</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62927; 83932</t>
+          <t>64427; 85173</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77691; 101496</t>
+          <t>77955; 101177</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>147801; 179048</t>
+          <t>147131; 178956</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>284750; 328568</t>
+          <t>286377; 329456</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>347770; 404953</t>
+          <t>348861; 404445</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>648831; 719338</t>
+          <t>646341; 719224</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2905_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,62; 62,44</t>
+          <t>43,09; 64,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,26; 65,21</t>
+          <t>48,01; 63,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,88; 60,83</t>
+          <t>48,18; 60,81</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,85%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,9; 63,14</t>
+          <t>48,25; 61,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,92; 60,58</t>
+          <t>48,83; 61,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,04; 60,43</t>
+          <t>50,26; 59,34</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,26; 48,92</t>
+          <t>34,7; 51,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,11; 52,23</t>
+          <t>32,25; 46,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,7; 48,18</t>
+          <t>36,29; 46,87</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,17; 53,11</t>
+          <t>43,45; 57,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,51; 57,77</t>
+          <t>41,13; 54,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,85; 53,34</t>
+          <t>44,56; 53,97</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,3; 53,26</t>
+          <t>46,79; 54,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,2; 54,73</t>
+          <t>45,94; 52,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,61; 52,98</t>
+          <t>47,36; 52,2</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62751</t>
+          <t>64343</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70151</t>
+          <t>64924</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132903</t>
+          <t>129267</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53836; 70596</t>
+          <t>52780; 78427</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56261; 88911</t>
+          <t>56044; 74587</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116911; 151727</t>
+          <t>115269; 145485</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>145</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>104033</t>
+          <t>125766</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>136122</t>
+          <t>98840</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>240155</t>
+          <t>224606</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92315; 116820</t>
+          <t>111013; 141472</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>120551; 149270</t>
+          <t>87598; 110509</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>220178; 260726</t>
+          <t>205804; 242969</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66055</t>
+          <t>69962</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80116</t>
+          <t>59134</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146171</t>
+          <t>129096</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>54851; 78330</t>
+          <t>57138; 83995</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67219; 94609</t>
+          <t>48688; 70183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128656; 164408</t>
+          <t>114561; 147939</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>74233</t>
+          <t>83023</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>76252</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163926</t>
+          <t>159276</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64427; 85173</t>
+          <t>71309; 93994</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77955; 101177</t>
+          <t>65666; 87386</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>147131; 178956</t>
+          <t>144270; 174736</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>448</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>307072</t>
+          <t>343094</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>376082</t>
+          <t>299151</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>642245</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>286377; 329456</t>
+          <t>318777; 369021</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>348861; 404445</t>
+          <t>278773; 321070</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646341; 719224</t>
+          <t>610007; 672454</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2905_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>52,53%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>55,61%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>43,09; 64,03</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>48,01; 63,89</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48,18; 60,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>54,66%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>55,1%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>48,25; 61,49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>48,83; 61,6</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>50,26; 59,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>42,49%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39,16%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>34,7; 51,01</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>32,25; 46,48</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36,29; 46,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>50,59%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>47,76%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>49,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>43,45; 57,27</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41,13; 54,73</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>44,56; 53,97</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>49,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>46,79; 54,16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>45,94; 52,91</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>47,36; 52,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.5252922793424525</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5561214165757379</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5403366983627815</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>64343</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>64924</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>129267</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4308998573631679</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4800571150724151</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4818242458135839</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>52780; 78427</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56044; 74587</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115269; 145485</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6402757407846632</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.638888472739114</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6081270431951202</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5466076210284017</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5509878574887804</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.548526577009297</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>125766</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>98840</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>224606</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4824871893454186</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4883161299326794</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5026105548439053</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>111013; 141472</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>87598; 110509</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>205804; 242969</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6148732020939455</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6160366347155646</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5933734019387359</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4248967924242317</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3916423786268468</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4089894851409175</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>69962</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>59134</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>129096</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.3470092450738678</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3224554919919376</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3629387820865018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>57138; 83995</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>48688; 70183</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>114561; 147939</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5101195295038522</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4648174495880826</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4686850170016987</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5059013008401725</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4776070740478944</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4919488653541382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>83023</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>76252</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>159276</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4345193463840652</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4113018947943118</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4456004279461378</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>71309; 93994</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>65666; 87386</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>144270; 174736</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5727490933231275</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5473440733338182</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5396998147417796</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.5035575957947974</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4930161237837379</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.4985919607301295</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>343094</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>299151</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>642245</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.4678663240910743</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4594324181200523</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4735648160470153</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>318777; 369021</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>278773; 321070</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>610007; 672454</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.5416091898780893</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5291393604674278</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5220439807616395</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>64343</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>64924</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>129267</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>52780</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>56044</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>115269</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>78427</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>74587</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>145485</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>125766</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>98840</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>224606</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>111013</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>87598</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>205804</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>141472</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>110509</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>242969</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>69962</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>59134</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>129096</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>57138</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>48688</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>114561</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>83995</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>70183</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>147939</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>83023</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>76252</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>159276</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>71309</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>65666</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>144270</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>93994</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>87386</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>174736</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>448</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>343094</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>299151</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>642245</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>318777</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>278773</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>610007</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>369021</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>321070</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>672454</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>